--- a/worklist_template_blank.xlsx
+++ b/worklist_template_blank.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01c1829094dbd390/Desktop/Kelly_Lab/.venv/worklist_git/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivint\OneDrive\Desktop\Kelly_Lab\.venv\worklist_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{E5540730-690F-444D-A5F0-1D8FDBE0762C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96077A02-DB05-4FE3-8A36-234DBAAA34D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75FC11C-46F6-45D4-B3B1-F2556627B923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{12DA0CF9-A1F3-4B47-B73A-18ED55D7EBC7}"/>
   </bookViews>
   <sheets>
-    <sheet name="User" sheetId="1" r:id="rId1"/>
-    <sheet name="Manager" sheetId="2" r:id="rId2"/>
+    <sheet name="Experiment" sheetId="1" r:id="rId1"/>
+    <sheet name="Machine" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
   <si>
     <t>Number:</t>
   </si>
@@ -171,9 +171,6 @@
     <t>Notebook Code:</t>
   </si>
   <si>
-    <t>A long set of instructions:</t>
-  </si>
-  <si>
     <t>Doesn't use all wells in order to create blocks of the same size.</t>
   </si>
   <si>
@@ -208,6 +205,18 @@
   </si>
   <si>
     <t>(choose)</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Autosampler Method:</t>
+  </si>
+  <si>
+    <t>Method Notes:</t>
+  </si>
+  <si>
+    <t>1 column</t>
   </si>
 </sst>
 </file>
@@ -256,7 +265,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -407,26 +416,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
@@ -493,16 +487,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -516,11 +502,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,10 +547,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A45856-9C0F-D140-AD60-2AFFFFA45290}">
-  <dimension ref="A1:AV63"/>
+  <dimension ref="A1:AU76"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -872,7 +878,7 @@
     <col min="30" max="30" width="8" customWidth="1"/>
     <col min="31" max="31" width="14.5" customWidth="1"/>
     <col min="33" max="33" width="12.33203125" customWidth="1"/>
-    <col min="34" max="34" width="11.6640625" customWidth="1"/>
+    <col min="34" max="34" width="17.33203125" customWidth="1"/>
     <col min="35" max="35" width="42" customWidth="1"/>
     <col min="36" max="36" width="21.1640625" customWidth="1"/>
     <col min="37" max="37" width="20.83203125" customWidth="1"/>
@@ -884,7 +890,7 @@
     <col min="43" max="45" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -899,12 +905,15 @@
         <v>2</v>
       </c>
       <c r="AG1" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM1" s="34"/>
+        <v>47</v>
+      </c>
+      <c r="AH1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM1" s="42"/>
       <c r="AO1" s="33"/>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
@@ -915,19 +924,22 @@
       <c r="AE2" s="8"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="29"/>
-      <c r="AI2" s="37" t="s">
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="10"/>
-      <c r="AK2" s="10"/>
-      <c r="AL2" s="10"/>
-      <c r="AM2" s="10"/>
-      <c r="AN2" s="10"/>
-      <c r="AO2" s="33"/>
-    </row>
-    <row r="3" spans="1:48" ht="16" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AL2" s="41"/>
+      <c r="AN2" s="33"/>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2"/>
       <c r="AD3" s="12">
@@ -936,19 +948,19 @@
       <c r="AE3" s="8"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="29"/>
-      <c r="AI3" s="37"/>
-      <c r="AJ3" s="10"/>
-      <c r="AK3" s="10"/>
-      <c r="AL3" s="10"/>
-      <c r="AM3" s="10"/>
-      <c r="AN3" s="10"/>
-      <c r="AO3" s="33"/>
-      <c r="AU3" s="36" t="s">
+      <c r="AH3" s="11"/>
+      <c r="AI3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AN3" s="33"/>
+      <c r="AT3" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="AV3" s="36"/>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AU3" s="39"/>
+    </row>
+    <row r="4" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
@@ -982,17 +994,13 @@
       <c r="AE4" s="8"/>
       <c r="AF4" s="7"/>
       <c r="AG4" s="29"/>
-      <c r="AI4" s="37"/>
-      <c r="AJ4" s="10"/>
-      <c r="AK4" s="10"/>
-      <c r="AL4" s="10"/>
-      <c r="AM4" s="10"/>
-      <c r="AN4" s="10"/>
-      <c r="AO4" s="33"/>
-      <c r="AU4" s="36"/>
-      <c r="AV4" s="36"/>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AH4" s="11"/>
+      <c r="AK4" s="23"/>
+      <c r="AN4" s="33"/>
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+    </row>
+    <row r="5" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -1080,17 +1088,22 @@
       <c r="AE5" s="8"/>
       <c r="AF5" s="7"/>
       <c r="AG5" s="29"/>
-      <c r="AI5" s="37"/>
-      <c r="AJ5" s="10"/>
-      <c r="AK5" s="10"/>
-      <c r="AL5" s="10"/>
-      <c r="AM5" s="10"/>
-      <c r="AN5" s="10"/>
-      <c r="AO5" s="33"/>
-      <c r="AU5" s="36"/>
-      <c r="AV5" s="36"/>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ5" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK5" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL5" s="44"/>
+      <c r="AN5" s="33"/>
+      <c r="AT5" s="39"/>
+      <c r="AU5" s="39"/>
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>39</v>
       </c>
@@ -1128,17 +1141,18 @@
       <c r="AE6" s="8"/>
       <c r="AF6" s="7"/>
       <c r="AG6" s="29"/>
-      <c r="AI6" s="37"/>
-      <c r="AJ6" s="10"/>
-      <c r="AK6" s="10"/>
-      <c r="AL6" s="10"/>
-      <c r="AM6" s="10"/>
-      <c r="AN6" s="10"/>
-      <c r="AO6" s="33"/>
-      <c r="AU6" s="36"/>
-      <c r="AV6" s="36"/>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ6" s="6"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="44"/>
+      <c r="AN6" s="33"/>
+      <c r="AT6" s="39"/>
+      <c r="AU6" s="39"/>
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D7" t="s">
         <v>14</v>
       </c>
@@ -1172,17 +1186,20 @@
       <c r="AE7" s="8"/>
       <c r="AF7" s="7"/>
       <c r="AG7" s="29"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="10"/>
-      <c r="AK7" s="10"/>
-      <c r="AL7" s="10"/>
-      <c r="AM7" s="10"/>
-      <c r="AN7" s="10"/>
-      <c r="AO7" s="33"/>
-      <c r="AU7" s="36"/>
-      <c r="AV7" s="36"/>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AH7" s="11"/>
+      <c r="AI7" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ7" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="44"/>
+      <c r="AN7" s="33"/>
+      <c r="AT7" s="39"/>
+      <c r="AU7" s="39"/>
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D8" t="s">
         <v>15</v>
       </c>
@@ -1216,17 +1233,16 @@
       <c r="AE8" s="8"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="29"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="10"/>
-      <c r="AK8" s="10"/>
-      <c r="AL8" s="10"/>
-      <c r="AM8" s="10"/>
-      <c r="AN8" s="10"/>
-      <c r="AO8" s="33"/>
-      <c r="AU8" s="36"/>
-      <c r="AV8" s="36"/>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="34"/>
+      <c r="AL8" s="34"/>
+      <c r="AN8" s="33"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="39"/>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
         <v>16</v>
       </c>
@@ -1260,17 +1276,17 @@
       <c r="AE9" s="8"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="29"/>
-      <c r="AI9" s="37"/>
+      <c r="AH9" s="11"/>
+      <c r="AI9" s="10"/>
       <c r="AJ9" s="10"/>
       <c r="AK9" s="10"/>
       <c r="AL9" s="10"/>
       <c r="AM9" s="10"/>
-      <c r="AN9" s="10"/>
-      <c r="AO9" s="33"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="36"/>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN9" s="33"/>
+      <c r="AT9" s="39"/>
+      <c r="AU9" s="39"/>
+    </row>
+    <row r="10" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D10" t="s">
         <v>17</v>
       </c>
@@ -1304,17 +1320,17 @@
       <c r="AE10" s="8"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="29"/>
-      <c r="AI10" s="37"/>
+      <c r="AH10" s="11"/>
+      <c r="AI10" s="10"/>
       <c r="AJ10" s="10"/>
       <c r="AK10" s="10"/>
       <c r="AL10" s="10"/>
       <c r="AM10" s="10"/>
-      <c r="AN10" s="10"/>
-      <c r="AO10" s="33"/>
-      <c r="AU10" s="36"/>
-      <c r="AV10" s="36"/>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN10" s="33"/>
+      <c r="AT10" s="39"/>
+      <c r="AU10" s="39"/>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
         <v>18</v>
       </c>
@@ -1348,17 +1364,17 @@
       <c r="AE11" s="8"/>
       <c r="AF11" s="7"/>
       <c r="AG11" s="29"/>
-      <c r="AI11" s="37"/>
+      <c r="AH11" s="11"/>
+      <c r="AI11" s="10"/>
       <c r="AJ11" s="10"/>
       <c r="AK11" s="10"/>
       <c r="AL11" s="10"/>
       <c r="AM11" s="10"/>
-      <c r="AN11" s="10"/>
-      <c r="AO11" s="33"/>
-      <c r="AU11" s="36"/>
-      <c r="AV11" s="36"/>
-    </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN11" s="33"/>
+      <c r="AT11" s="39"/>
+      <c r="AU11" s="39"/>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>19</v>
       </c>
@@ -1392,17 +1408,17 @@
       <c r="AE12" s="8"/>
       <c r="AF12" s="7"/>
       <c r="AG12" s="29"/>
-      <c r="AI12" s="37"/>
+      <c r="AH12" s="11"/>
+      <c r="AI12" s="10"/>
       <c r="AJ12" s="10"/>
       <c r="AK12" s="10"/>
       <c r="AL12" s="10"/>
       <c r="AM12" s="10"/>
-      <c r="AN12" s="10"/>
-      <c r="AO12" s="33"/>
-      <c r="AU12" s="36"/>
-      <c r="AV12" s="36"/>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN12" s="33"/>
+      <c r="AT12" s="39"/>
+      <c r="AU12" s="39"/>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
         <v>20</v>
       </c>
@@ -1436,17 +1452,17 @@
       <c r="AE13" s="8"/>
       <c r="AF13" s="7"/>
       <c r="AG13" s="29"/>
-      <c r="AI13" s="37"/>
+      <c r="AH13" s="11"/>
+      <c r="AI13" s="10"/>
       <c r="AJ13" s="10"/>
       <c r="AK13" s="10"/>
       <c r="AL13" s="10"/>
       <c r="AM13" s="10"/>
-      <c r="AN13" s="10"/>
-      <c r="AO13" s="33"/>
-      <c r="AU13" s="36"/>
-      <c r="AV13" s="36"/>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN13" s="33"/>
+      <c r="AT13" s="39"/>
+      <c r="AU13" s="39"/>
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
         <v>21</v>
       </c>
@@ -1480,17 +1496,17 @@
       <c r="AE14" s="8"/>
       <c r="AF14" s="7"/>
       <c r="AG14" s="29"/>
-      <c r="AI14" s="37"/>
+      <c r="AH14" s="11"/>
+      <c r="AI14" s="10"/>
       <c r="AJ14" s="10"/>
       <c r="AK14" s="10"/>
       <c r="AL14" s="10"/>
       <c r="AM14" s="10"/>
-      <c r="AN14" s="10"/>
-      <c r="AO14" s="33"/>
-      <c r="AU14" s="36"/>
-      <c r="AV14" s="36"/>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN14" s="33"/>
+      <c r="AT14" s="39"/>
+      <c r="AU14" s="39"/>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
         <v>22</v>
       </c>
@@ -1524,15 +1540,15 @@
       <c r="AE15" s="8"/>
       <c r="AF15" s="7"/>
       <c r="AG15" s="29"/>
-      <c r="AI15" s="37"/>
+      <c r="AH15" s="11"/>
+      <c r="AI15" s="10"/>
       <c r="AJ15" s="10"/>
       <c r="AK15" s="10"/>
       <c r="AL15" s="10"/>
       <c r="AM15" s="10"/>
-      <c r="AN15" s="10"/>
-      <c r="AO15" s="33"/>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.4">
+      <c r="AN15" s="33"/>
+    </row>
+    <row r="16" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D16" t="s">
         <v>23</v>
       </c>
@@ -1566,13 +1582,13 @@
       <c r="AE16" s="8"/>
       <c r="AF16" s="7"/>
       <c r="AG16" s="29"/>
-      <c r="AI16" s="37"/>
+      <c r="AH16" s="11"/>
+      <c r="AI16" s="10"/>
       <c r="AJ16" s="10"/>
       <c r="AK16" s="10"/>
       <c r="AL16" s="10"/>
       <c r="AM16" s="10"/>
-      <c r="AN16" s="10"/>
-      <c r="AO16" s="33"/>
+      <c r="AN16" s="33"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
@@ -1608,13 +1624,13 @@
       <c r="AE17" s="8"/>
       <c r="AF17" s="7"/>
       <c r="AG17" s="29"/>
-      <c r="AI17" s="37"/>
+      <c r="AH17" s="11"/>
+      <c r="AI17" s="10"/>
       <c r="AJ17" s="10"/>
       <c r="AK17" s="10"/>
       <c r="AL17" s="10"/>
       <c r="AM17" s="10"/>
-      <c r="AN17" s="10"/>
-      <c r="AO17" s="33"/>
+      <c r="AN17" s="33"/>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
@@ -1650,13 +1666,13 @@
       <c r="AE18" s="8"/>
       <c r="AF18" s="7"/>
       <c r="AG18" s="29"/>
-      <c r="AI18" s="37"/>
+      <c r="AH18" s="11"/>
+      <c r="AI18" s="10"/>
       <c r="AJ18" s="10"/>
       <c r="AK18" s="10"/>
       <c r="AL18" s="10"/>
       <c r="AM18" s="10"/>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="33"/>
+      <c r="AN18" s="33"/>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
@@ -1692,13 +1708,13 @@
       <c r="AE19" s="8"/>
       <c r="AF19" s="7"/>
       <c r="AG19" s="29"/>
-      <c r="AI19" s="37"/>
+      <c r="AH19" s="11"/>
+      <c r="AI19" s="10"/>
       <c r="AJ19" s="10"/>
       <c r="AK19" s="10"/>
       <c r="AL19" s="10"/>
       <c r="AM19" s="10"/>
-      <c r="AN19" s="10"/>
-      <c r="AO19" s="33"/>
+      <c r="AN19" s="33"/>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
@@ -1734,13 +1750,13 @@
       <c r="AE20" s="8"/>
       <c r="AF20" s="7"/>
       <c r="AG20" s="29"/>
-      <c r="AI20" s="37"/>
+      <c r="AH20" s="11"/>
+      <c r="AI20" s="10"/>
       <c r="AJ20" s="10"/>
       <c r="AK20" s="10"/>
       <c r="AL20" s="10"/>
       <c r="AM20" s="10"/>
-      <c r="AN20" s="10"/>
-      <c r="AO20" s="33"/>
+      <c r="AN20" s="33"/>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
@@ -1776,13 +1792,13 @@
       <c r="AE21" s="8"/>
       <c r="AF21" s="7"/>
       <c r="AG21" s="29"/>
-      <c r="AI21" s="37"/>
+      <c r="AH21" s="11"/>
+      <c r="AI21" s="10"/>
       <c r="AJ21" s="10"/>
       <c r="AK21" s="10"/>
       <c r="AL21" s="10"/>
       <c r="AM21" s="10"/>
-      <c r="AN21" s="10"/>
-      <c r="AO21" s="33"/>
+      <c r="AN21" s="33"/>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A22" s="3"/>
@@ -1818,13 +1834,13 @@
       <c r="AE22" s="8"/>
       <c r="AF22" s="7"/>
       <c r="AG22" s="29"/>
-      <c r="AI22" s="37"/>
+      <c r="AH22" s="11"/>
+      <c r="AI22" s="10"/>
       <c r="AJ22" s="10"/>
       <c r="AK22" s="10"/>
       <c r="AL22" s="10"/>
       <c r="AM22" s="10"/>
-      <c r="AN22" s="10"/>
-      <c r="AO22" s="33"/>
+      <c r="AN22" s="33"/>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
@@ -1914,13 +1930,13 @@
       <c r="AE23" s="8"/>
       <c r="AF23" s="7"/>
       <c r="AG23" s="29"/>
-      <c r="AI23" s="37"/>
+      <c r="AH23" s="11"/>
+      <c r="AI23" s="10"/>
       <c r="AJ23" s="10"/>
       <c r="AK23" s="10"/>
       <c r="AL23" s="10"/>
       <c r="AM23" s="10"/>
-      <c r="AN23" s="10"/>
-      <c r="AO23" s="33"/>
+      <c r="AN23" s="33"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
@@ -1960,13 +1976,13 @@
       <c r="AE24" s="8"/>
       <c r="AF24" s="7"/>
       <c r="AG24" s="29"/>
-      <c r="AI24" s="37"/>
+      <c r="AH24" s="11"/>
+      <c r="AI24" s="10"/>
       <c r="AJ24" s="10"/>
       <c r="AK24" s="10"/>
       <c r="AL24" s="10"/>
       <c r="AM24" s="10"/>
-      <c r="AN24" s="10"/>
-      <c r="AO24" s="33"/>
+      <c r="AN24" s="33"/>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
@@ -2002,13 +2018,13 @@
       <c r="AE25" s="8"/>
       <c r="AF25" s="7"/>
       <c r="AG25" s="29"/>
-      <c r="AI25" s="37"/>
+      <c r="AH25" s="11"/>
+      <c r="AI25" s="10"/>
       <c r="AJ25" s="10"/>
       <c r="AK25" s="10"/>
       <c r="AL25" s="10"/>
       <c r="AM25" s="10"/>
-      <c r="AN25" s="10"/>
-      <c r="AO25" s="33"/>
+      <c r="AN25" s="33"/>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D26" t="s">
@@ -2044,13 +2060,13 @@
       <c r="AE26" s="8"/>
       <c r="AF26" s="7"/>
       <c r="AG26" s="29"/>
-      <c r="AI26" s="37"/>
+      <c r="AH26" s="11"/>
+      <c r="AI26" s="10"/>
       <c r="AJ26" s="10"/>
       <c r="AK26" s="10"/>
       <c r="AL26" s="10"/>
       <c r="AM26" s="10"/>
-      <c r="AN26" s="10"/>
-      <c r="AO26" s="33"/>
+      <c r="AN26" s="33"/>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D27" t="s">
@@ -2086,13 +2102,13 @@
       <c r="AE27" s="8"/>
       <c r="AF27" s="7"/>
       <c r="AG27" s="29"/>
-      <c r="AI27" s="37"/>
+      <c r="AH27" s="11"/>
+      <c r="AI27" s="10"/>
       <c r="AJ27" s="10"/>
       <c r="AK27" s="10"/>
       <c r="AL27" s="10"/>
       <c r="AM27" s="10"/>
-      <c r="AN27" s="10"/>
-      <c r="AO27" s="33"/>
+      <c r="AN27" s="33"/>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D28" t="s">
@@ -2128,13 +2144,13 @@
       <c r="AE28" s="8"/>
       <c r="AF28" s="7"/>
       <c r="AG28" s="29"/>
-      <c r="AI28" s="37"/>
+      <c r="AH28" s="11"/>
+      <c r="AI28" s="10"/>
       <c r="AJ28" s="10"/>
       <c r="AK28" s="10"/>
       <c r="AL28" s="10"/>
       <c r="AM28" s="10"/>
-      <c r="AN28" s="10"/>
-      <c r="AO28" s="33"/>
+      <c r="AN28" s="33"/>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
@@ -2170,13 +2186,13 @@
       <c r="AE29" s="8"/>
       <c r="AF29" s="7"/>
       <c r="AG29" s="29"/>
-      <c r="AI29" s="37"/>
+      <c r="AH29" s="11"/>
+      <c r="AI29" s="10"/>
       <c r="AJ29" s="10"/>
       <c r="AK29" s="10"/>
       <c r="AL29" s="10"/>
       <c r="AM29" s="10"/>
-      <c r="AN29" s="10"/>
-      <c r="AO29" s="33"/>
+      <c r="AN29" s="33"/>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D30" t="s">
@@ -2212,13 +2228,13 @@
       <c r="AE30" s="8"/>
       <c r="AF30" s="7"/>
       <c r="AG30" s="29"/>
-      <c r="AI30" s="37"/>
+      <c r="AH30" s="11"/>
+      <c r="AI30" s="10"/>
       <c r="AJ30" s="10"/>
       <c r="AK30" s="10"/>
       <c r="AL30" s="10"/>
       <c r="AM30" s="10"/>
-      <c r="AN30" s="10"/>
-      <c r="AO30" s="33"/>
+      <c r="AN30" s="33"/>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D31" t="s">
@@ -2254,13 +2270,13 @@
       <c r="AE31" s="8"/>
       <c r="AF31" s="7"/>
       <c r="AG31" s="29"/>
-      <c r="AI31" s="37"/>
-      <c r="AJ31" s="10"/>
-      <c r="AK31" s="10"/>
-      <c r="AL31" s="10"/>
+      <c r="AH31" s="11"/>
+      <c r="AI31" s="45"/>
+      <c r="AJ31" s="45"/>
+      <c r="AK31" s="45"/>
+      <c r="AL31" s="45"/>
       <c r="AM31" s="10"/>
-      <c r="AN31" s="10"/>
-      <c r="AO31" s="33"/>
+      <c r="AN31" s="33"/>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D32" t="s">
@@ -2296,10 +2312,11 @@
       <c r="AE32" s="8"/>
       <c r="AF32" s="7"/>
       <c r="AG32" s="29"/>
-      <c r="AI32" s="10"/>
-      <c r="AJ32" s="10"/>
-      <c r="AK32" s="10"/>
-      <c r="AL32" s="10"/>
+      <c r="AH32" s="11"/>
+      <c r="AI32" s="45"/>
+      <c r="AJ32" s="45"/>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
       <c r="AM32" s="10"/>
       <c r="AN32" s="10"/>
       <c r="AO32" s="33"/>
@@ -2338,16 +2355,11 @@
       <c r="AE33" s="8"/>
       <c r="AF33" s="7"/>
       <c r="AG33" s="29"/>
-      <c r="AI33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ33" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK33" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL33" s="43"/>
+      <c r="AH33" s="11"/>
+      <c r="AI33" s="42"/>
+      <c r="AJ33" s="42"/>
+      <c r="AK33" s="44"/>
+      <c r="AL33" s="44"/>
       <c r="AM33" s="10"/>
       <c r="AN33" s="10"/>
       <c r="AO33" s="33"/>
@@ -2386,11 +2398,11 @@
       <c r="AE34" s="12"/>
       <c r="AF34" s="11"/>
       <c r="AG34" s="11"/>
-      <c r="AI34" t="s">
-        <v>55</v>
-      </c>
-      <c r="AK34" s="43"/>
-      <c r="AL34" s="43"/>
+      <c r="AH34" s="11"/>
+      <c r="AI34" s="42"/>
+      <c r="AJ34" s="42"/>
+      <c r="AK34" s="44"/>
+      <c r="AL34" s="44"/>
     </row>
     <row r="35" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D35" t="s">
@@ -2426,7 +2438,11 @@
       <c r="AE35" s="12"/>
       <c r="AF35" s="11"/>
       <c r="AG35" s="11"/>
-      <c r="AK35" s="23"/>
+      <c r="AH35" s="11"/>
+      <c r="AI35" s="42"/>
+      <c r="AJ35" s="42"/>
+      <c r="AK35" s="46"/>
+      <c r="AL35" s="42"/>
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D36" t="s">
@@ -2462,16 +2478,11 @@
       <c r="AE36" s="12"/>
       <c r="AF36" s="11"/>
       <c r="AG36" s="11"/>
-      <c r="AI36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ36" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK36" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL36" s="43"/>
+      <c r="AH36" s="11"/>
+      <c r="AI36" s="42"/>
+      <c r="AJ36" s="47"/>
+      <c r="AK36" s="44"/>
+      <c r="AL36" s="44"/>
     </row>
     <row r="37" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D37" t="s">
@@ -2507,12 +2518,11 @@
       <c r="AE37" s="12"/>
       <c r="AF37" s="11"/>
       <c r="AG37" s="11"/>
-      <c r="AI37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ37" s="6"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="43"/>
+      <c r="AH37" s="11"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="44"/>
+      <c r="AL37" s="44"/>
     </row>
     <row r="38" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D38" t="s">
@@ -2548,14 +2558,11 @@
       <c r="AE38" s="12"/>
       <c r="AF38" s="11"/>
       <c r="AG38" s="11"/>
-      <c r="AI38" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ38" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK38" s="42"/>
-      <c r="AL38" s="43"/>
+      <c r="AH38" s="11"/>
+      <c r="AI38" s="48"/>
+      <c r="AJ38" s="49"/>
+      <c r="AK38" s="44"/>
+      <c r="AL38" s="44"/>
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D39" t="s">
@@ -2591,10 +2598,11 @@
       <c r="AE39" s="12"/>
       <c r="AF39" s="11"/>
       <c r="AG39" s="11"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="41"/>
-      <c r="AK39" s="35"/>
-      <c r="AL39" s="35"/>
+      <c r="AH39" s="11"/>
+      <c r="AI39" s="48"/>
+      <c r="AJ39" s="49"/>
+      <c r="AK39" s="50"/>
+      <c r="AL39" s="50"/>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A40" s="3"/>
@@ -2630,8 +2638,11 @@
       <c r="AE40" s="12"/>
       <c r="AF40" s="11"/>
       <c r="AG40" s="11"/>
-      <c r="AJ40" s="35"/>
-      <c r="AK40" s="35"/>
+      <c r="AH40" s="11"/>
+      <c r="AI40" s="42"/>
+      <c r="AJ40" s="50"/>
+      <c r="AK40" s="50"/>
+      <c r="AL40" s="42"/>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
@@ -2721,8 +2732,11 @@
       <c r="AE41" s="12"/>
       <c r="AF41" s="11"/>
       <c r="AG41" s="11"/>
-      <c r="AJ41" s="35"/>
-      <c r="AK41" s="35"/>
+      <c r="AH41" s="11"/>
+      <c r="AI41" s="42"/>
+      <c r="AJ41" s="50"/>
+      <c r="AK41" s="50"/>
+      <c r="AL41" s="42"/>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A42" s="13" t="s">
@@ -2762,6 +2776,11 @@
       <c r="AE42" s="12"/>
       <c r="AF42" s="11"/>
       <c r="AG42" s="11"/>
+      <c r="AH42" s="11"/>
+      <c r="AI42" s="42"/>
+      <c r="AJ42" s="42"/>
+      <c r="AK42" s="42"/>
+      <c r="AL42" s="42"/>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D43" t="s">
@@ -2797,6 +2816,7 @@
       <c r="AE43" s="12"/>
       <c r="AF43" s="11"/>
       <c r="AG43" s="11"/>
+      <c r="AH43" s="11"/>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D44" t="s">
@@ -2832,6 +2852,7 @@
       <c r="AE44" s="8"/>
       <c r="AF44" s="11"/>
       <c r="AG44" s="11"/>
+      <c r="AH44" s="11"/>
     </row>
     <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D45" t="s">
@@ -2867,6 +2888,7 @@
       <c r="AE45" s="12"/>
       <c r="AF45" s="11"/>
       <c r="AG45" s="11"/>
+      <c r="AH45" s="11"/>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D46" t="s">
@@ -2902,6 +2924,7 @@
       <c r="AE46" s="8"/>
       <c r="AF46" s="11"/>
       <c r="AG46" s="11"/>
+      <c r="AH46" s="11"/>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D47" t="s">
@@ -2937,6 +2960,7 @@
       <c r="AE47" s="12"/>
       <c r="AF47" s="11"/>
       <c r="AG47" s="11"/>
+      <c r="AH47" s="11"/>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D48" t="s">
@@ -2972,6 +2996,7 @@
       <c r="AE48" s="12"/>
       <c r="AF48" s="27"/>
       <c r="AG48" s="11"/>
+      <c r="AH48" s="11"/>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D49" t="s">
@@ -3007,6 +3032,7 @@
       <c r="AE49" s="12"/>
       <c r="AF49" s="27"/>
       <c r="AG49" s="11"/>
+      <c r="AH49" s="11"/>
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D50" t="s">
@@ -3042,6 +3068,7 @@
       <c r="AE50" s="12"/>
       <c r="AF50" s="27"/>
       <c r="AG50" s="11"/>
+      <c r="AH50" s="11"/>
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D51" t="s">
@@ -3077,6 +3104,7 @@
       <c r="AE51" s="20"/>
       <c r="AF51" s="21"/>
       <c r="AG51" s="21"/>
+      <c r="AH51" s="21"/>
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D52" t="s">
@@ -3305,6 +3333,87 @@
       <c r="AN58" s="23"/>
     </row>
     <row r="59" spans="1:40" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>6</v>
+      </c>
+      <c r="K59">
+        <v>7</v>
+      </c>
+      <c r="L59">
+        <v>8</v>
+      </c>
+      <c r="M59">
+        <v>9</v>
+      </c>
+      <c r="N59">
+        <v>10</v>
+      </c>
+      <c r="O59">
+        <v>11</v>
+      </c>
+      <c r="P59">
+        <v>12</v>
+      </c>
+      <c r="Q59">
+        <v>13</v>
+      </c>
+      <c r="R59">
+        <v>14</v>
+      </c>
+      <c r="S59">
+        <v>15</v>
+      </c>
+      <c r="T59">
+        <v>16</v>
+      </c>
+      <c r="U59">
+        <v>17</v>
+      </c>
+      <c r="V59">
+        <v>18</v>
+      </c>
+      <c r="W59">
+        <v>19</v>
+      </c>
+      <c r="X59">
+        <v>20</v>
+      </c>
+      <c r="Y59">
+        <v>21</v>
+      </c>
+      <c r="Z59">
+        <v>22</v>
+      </c>
+      <c r="AA59">
+        <v>23</v>
+      </c>
+      <c r="AB59">
+        <v>24</v>
+      </c>
       <c r="AE59" s="10"/>
       <c r="AK59" s="23"/>
       <c r="AL59" s="24"/>
@@ -3312,36 +3421,526 @@
       <c r="AN59" s="23"/>
     </row>
     <row r="60" spans="1:40" x14ac:dyDescent="0.4">
+      <c r="A60" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="14"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
+      <c r="R60" s="15"/>
+      <c r="S60" s="15"/>
+      <c r="T60" s="15"/>
+      <c r="U60" s="15"/>
+      <c r="V60" s="15"/>
+      <c r="W60" s="15"/>
+      <c r="X60" s="15"/>
+      <c r="Y60" s="15"/>
+      <c r="Z60" s="15"/>
+      <c r="AA60" s="15"/>
+      <c r="AB60" s="16"/>
       <c r="AE60" s="10"/>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.4">
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="8"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="10"/>
+      <c r="Z61" s="10"/>
+      <c r="AA61" s="10"/>
+      <c r="AB61" s="9"/>
       <c r="AE61" s="10"/>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.4">
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
+      <c r="Z62" s="10"/>
+      <c r="AA62" s="10"/>
+      <c r="AB62" s="9"/>
       <c r="AE62" s="10"/>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.4">
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="8"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="10"/>
+      <c r="X63" s="10"/>
+      <c r="Y63" s="10"/>
+      <c r="Z63" s="10"/>
+      <c r="AA63" s="10"/>
+      <c r="AB63" s="9"/>
       <c r="AE63" s="10"/>
+    </row>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.4">
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="10"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="10"/>
+      <c r="Y64" s="10"/>
+      <c r="Z64" s="10"/>
+      <c r="AA64" s="10"/>
+      <c r="AB64" s="9"/>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
+      <c r="V65" s="10"/>
+      <c r="W65" s="10"/>
+      <c r="X65" s="10"/>
+      <c r="Y65" s="10"/>
+      <c r="Z65" s="10"/>
+      <c r="AA65" s="10"/>
+      <c r="AB65" s="9"/>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="10"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="10"/>
+      <c r="Y66" s="10"/>
+      <c r="Z66" s="10"/>
+      <c r="AA66" s="10"/>
+      <c r="AB66" s="9"/>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
+      <c r="V67" s="10"/>
+      <c r="W67" s="10"/>
+      <c r="X67" s="10"/>
+      <c r="Y67" s="10"/>
+      <c r="Z67" s="10"/>
+      <c r="AA67" s="10"/>
+      <c r="AB67" s="9"/>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="10"/>
+      <c r="X68" s="10"/>
+      <c r="Y68" s="10"/>
+      <c r="Z68" s="10"/>
+      <c r="AA68" s="10"/>
+      <c r="AB68" s="9"/>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="10"/>
+      <c r="X69" s="10"/>
+      <c r="Y69" s="10"/>
+      <c r="Z69" s="10"/>
+      <c r="AA69" s="10"/>
+      <c r="AB69" s="9"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="10"/>
+      <c r="Y70" s="10"/>
+      <c r="Z70" s="10"/>
+      <c r="AA70" s="10"/>
+      <c r="AB70" s="9"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="10"/>
+      <c r="Y71" s="10"/>
+      <c r="Z71" s="10"/>
+      <c r="AA71" s="10"/>
+      <c r="AB71" s="9"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D72" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="10"/>
+      <c r="X72" s="10"/>
+      <c r="Y72" s="10"/>
+      <c r="Z72" s="10"/>
+      <c r="AA72" s="10"/>
+      <c r="AB72" s="9"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="10"/>
+      <c r="X73" s="10"/>
+      <c r="Y73" s="10"/>
+      <c r="Z73" s="10"/>
+      <c r="AA73" s="10"/>
+      <c r="AB73" s="9"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="10"/>
+      <c r="U74" s="10"/>
+      <c r="V74" s="10"/>
+      <c r="W74" s="10"/>
+      <c r="X74" s="10"/>
+      <c r="Y74" s="10"/>
+      <c r="Z74" s="10"/>
+      <c r="AA74" s="10"/>
+      <c r="AB74" s="9"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="18"/>
+      <c r="R75" s="18"/>
+      <c r="S75" s="18"/>
+      <c r="T75" s="18"/>
+      <c r="U75" s="18"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="18"/>
+      <c r="X75" s="18"/>
+      <c r="Y75" s="18"/>
+      <c r="Z75" s="18"/>
+      <c r="AA75" s="18"/>
+      <c r="AB75" s="19"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="6">
-    <mergeCell ref="AU3:AV14"/>
-    <mergeCell ref="AI2:AI31"/>
+  <mergeCells count="7">
+    <mergeCell ref="AT3:AU14"/>
     <mergeCell ref="AI38:AI39"/>
     <mergeCell ref="AJ38:AJ39"/>
     <mergeCell ref="AK36:AL38"/>
     <mergeCell ref="AK33:AL34"/>
+    <mergeCell ref="AK5:AL7"/>
+    <mergeCell ref="AK2:AL3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE51" xr:uid="{F021A723-187F-DD4D-8685-6A2D324FBA89}">
       <formula1>"Condition,QC,Blank,TrueBlank,Lib,SystemValidation,WetQC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A24 A42 A6" xr:uid="{77917AAB-E5BC-9D49-9737-341DECD5F2E8}">
-      <formula1>"R,G,B"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 A60 A42 A24" xr:uid="{77917AAB-E5BC-9D49-9737-341DECD5F2E8}">
+      <formula1>"R,G,B,Y"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ33 AJ38:AJ39" xr:uid="{FA86A04D-C042-8741-AB64-AFB417F744D7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ33 AJ38:AJ39 AJ2 AJ7:AJ8" xr:uid="{FA86A04D-C042-8741-AB64-AFB417F744D7}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3352,1493 +3951,1697 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA40715-6F6B-5649-8058-60881427272C}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="1" max="1" width="13.9140625" customWidth="1"/>
     <col min="17" max="17" width="29.33203125" customWidth="1"/>
     <col min="18" max="18" width="24.6640625" customWidth="1"/>
     <col min="19" max="19" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="G1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="K1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="M1" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A2" t="str">
+        <f>IF(Experiment!AH2="","",Experiment!AH2)</f>
+        <v/>
+      </c>
+      <c r="B2" s="12">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <f>IF(LEN(Experiment!AE2)=0,"",Experiment!AE2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="7" t="str">
+        <f>IF(LEN(Experiment!AF2)=0,"",Experiment!AF2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="29" t="str">
+        <f>IF(LEN(Experiment!AG2)=0,"",Experiment!AG2)</f>
+        <v/>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="11"/>
+      <c r="R2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A3" t="str">
+        <f>IF(Experiment!AH3="","",Experiment!AH3)</f>
+        <v/>
+      </c>
+      <c r="B3" s="12">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <f>IF(LEN(Experiment!AE3)=0,"",Experiment!AE3)</f>
+        <v/>
+      </c>
+      <c r="D3" s="7" t="str">
+        <f>IF(LEN(Experiment!AF3)=0,"",Experiment!AF3)</f>
+        <v/>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="29" t="str">
+        <f>IF(LEN(Experiment!AG3)=0,"",Experiment!AG3)</f>
+        <v/>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A4" t="str">
+        <f>IF(Experiment!AH4="","",Experiment!AH4)</f>
+        <v/>
+      </c>
+      <c r="B4" s="12">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <f>IF(LEN(Experiment!AE4)=0,"",Experiment!AE4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="7" t="str">
+        <f>IF(LEN(Experiment!AF4)=0,"",Experiment!AF4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="29" t="str">
+        <f>IF(LEN(Experiment!AG4)=0,"",Experiment!AG4)</f>
+        <v/>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="11"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="24"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A5" t="str">
+        <f>IF(Experiment!AH5="","",Experiment!AH5)</f>
+        <v/>
+      </c>
+      <c r="B5" s="12">
+        <v>4</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <f>IF(LEN(Experiment!AE5)=0,"",Experiment!AE5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="7" t="str">
+        <f>IF(LEN(Experiment!AF5)=0,"",Experiment!AF5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="29" t="str">
+        <f>IF(LEN(Experiment!AG5)=0,"",Experiment!AG5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="11"/>
+      <c r="R5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="S5" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A6" t="str">
+        <f>IF(Experiment!AH6="","",Experiment!AH6)</f>
+        <v/>
+      </c>
+      <c r="B6" s="12">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f>IF(LEN(Experiment!AE6)=0,"",Experiment!AE6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7" t="str">
+        <f>IF(LEN(Experiment!AF6)=0,"",Experiment!AF6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="29" t="str">
+        <f>IF(LEN(Experiment!AG6)=0,"",Experiment!AG6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="11"/>
+      <c r="R6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="32"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A7" t="str">
+        <f>IF(Experiment!AH7="","",Experiment!AH7)</f>
+        <v/>
+      </c>
+      <c r="B7" s="12">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f>IF(LEN(Experiment!AE7)=0,"",Experiment!AE7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="7" t="str">
+        <f>IF(LEN(Experiment!AF7)=0,"",Experiment!AF7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="29" t="str">
+        <f>IF(LEN(Experiment!AG7)=0,"",Experiment!AG7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="11"/>
+      <c r="R7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S7" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A8" t="str">
+        <f>IF(Experiment!AH8="","",Experiment!AH8)</f>
+        <v/>
+      </c>
+      <c r="B8" s="12">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f>IF(LEN(Experiment!AE8)=0,"",Experiment!AE8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="7" t="str">
+        <f>IF(LEN(Experiment!AF8)=0,"",Experiment!AF8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="29" t="str">
+        <f>IF(LEN(Experiment!AG8)=0,"",Experiment!AG8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="11"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A9" t="str">
+        <f>IF(Experiment!AH9="","",Experiment!AH9)</f>
+        <v/>
+      </c>
+      <c r="B9" s="12">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <f>IF(LEN(Experiment!AE9)=0,"",Experiment!AE9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f>IF(LEN(Experiment!AF9)=0,"",Experiment!AF9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="29" t="str">
+        <f>IF(LEN(Experiment!AG9)=0,"",Experiment!AG9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="11"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A10" t="str">
+        <f>IF(Experiment!AH10="","",Experiment!AH10)</f>
+        <v/>
+      </c>
+      <c r="B10" s="12">
         <v>9</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="C10" s="8" t="str">
+        <f>IF(LEN(Experiment!AE10)=0,"",Experiment!AE10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="7" t="str">
+        <f>IF(LEN(Experiment!AF10)=0,"",Experiment!AF10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="29" t="str">
+        <f>IF(LEN(Experiment!AG10)=0,"",Experiment!AG10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="11"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A11" t="str">
+        <f>IF(Experiment!AH11="","",Experiment!AH11)</f>
+        <v/>
+      </c>
+      <c r="B11" s="12">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <f>IF(LEN(Experiment!AE11)=0,"",Experiment!AE11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7" t="str">
+        <f>IF(LEN(Experiment!AF11)=0,"",Experiment!AF11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="29" t="str">
+        <f>IF(LEN(Experiment!AG11)=0,"",Experiment!AG11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="11"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A12" t="str">
+        <f>IF(Experiment!AH12="","",Experiment!AH12)</f>
+        <v/>
+      </c>
+      <c r="B12" s="12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f>IF(LEN(Experiment!AE12)=0,"",Experiment!AE12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="str">
+        <f>IF(LEN(Experiment!AF12)=0,"",Experiment!AF12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="29" t="str">
+        <f>IF(LEN(Experiment!AG12)=0,"",Experiment!AG12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A13" t="str">
+        <f>IF(Experiment!AH13="","",Experiment!AH13)</f>
+        <v/>
+      </c>
+      <c r="B13" s="12">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f>IF(LEN(Experiment!AE13)=0,"",Experiment!AE13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="7" t="str">
+        <f>IF(LEN(Experiment!AF13)=0,"",Experiment!AF13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="29" t="str">
+        <f>IF(LEN(Experiment!AG13)=0,"",Experiment!AG13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="11"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A14" t="str">
+        <f>IF(Experiment!AH14="","",Experiment!AH14)</f>
+        <v/>
+      </c>
+      <c r="B14" s="12">
+        <v>13</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f>IF(LEN(Experiment!AE14)=0,"",Experiment!AE14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="str">
+        <f>IF(LEN(Experiment!AF14)=0,"",Experiment!AF14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="29" t="str">
+        <f>IF(LEN(Experiment!AG14)=0,"",Experiment!AG14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="11"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A15" t="str">
+        <f>IF(Experiment!AH15="","",Experiment!AH15)</f>
+        <v/>
+      </c>
+      <c r="B15" s="12">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f>IF(LEN(Experiment!AE15)=0,"",Experiment!AE15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="7" t="str">
+        <f>IF(LEN(Experiment!AF15)=0,"",Experiment!AF15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="29" t="str">
+        <f>IF(LEN(Experiment!AG15)=0,"",Experiment!AG15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="11"/>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" t="str">
+        <f>IF(Experiment!AH16="","",Experiment!AH16)</f>
+        <v/>
+      </c>
+      <c r="B16" s="12">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f>IF(LEN(Experiment!AE16)=0,"",Experiment!AE16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="7" t="str">
+        <f>IF(LEN(Experiment!AF16)=0,"",Experiment!AF16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="29" t="str">
+        <f>IF(LEN(Experiment!AG16)=0,"",Experiment!AG16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="11"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A17" t="str">
+        <f>IF(Experiment!AH17="","",Experiment!AH17)</f>
+        <v/>
+      </c>
+      <c r="B17" s="12">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f>IF(LEN(Experiment!AE17)=0,"",Experiment!AE17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="7" t="str">
+        <f>IF(LEN(Experiment!AF17)=0,"",Experiment!AF17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="29" t="str">
+        <f>IF(LEN(Experiment!AG17)=0,"",Experiment!AG17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="11"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A18" t="str">
+        <f>IF(Experiment!AH18="","",Experiment!AH18)</f>
+        <v/>
+      </c>
+      <c r="B18" s="12">
+        <v>17</v>
+      </c>
+      <c r="C18" s="8" t="str">
+        <f>IF(LEN(Experiment!AE18)=0,"",Experiment!AE18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="7" t="str">
+        <f>IF(LEN(Experiment!AF18)=0,"",Experiment!AF18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="29" t="str">
+        <f>IF(LEN(Experiment!AG18)=0,"",Experiment!AG18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A19" t="str">
+        <f>IF(Experiment!AH19="","",Experiment!AH19)</f>
+        <v/>
+      </c>
+      <c r="B19" s="12">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="str">
+        <f>IF(LEN(Experiment!AE19)=0,"",Experiment!AE19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="7" t="str">
+        <f>IF(LEN(Experiment!AF19)=0,"",Experiment!AF19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="29" t="str">
+        <f>IF(LEN(Experiment!AG19)=0,"",Experiment!AG19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A20" t="str">
+        <f>IF(Experiment!AH20="","",Experiment!AH20)</f>
+        <v/>
+      </c>
+      <c r="B20" s="12">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8" t="str">
+        <f>IF(LEN(Experiment!AE20)=0,"",Experiment!AE20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="7" t="str">
+        <f>IF(LEN(Experiment!AF20)=0,"",Experiment!AF20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="29" t="str">
+        <f>IF(LEN(Experiment!AG20)=0,"",Experiment!AG20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="11"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A21" t="str">
+        <f>IF(Experiment!AH21="","",Experiment!AH21)</f>
+        <v/>
+      </c>
+      <c r="B21" s="12">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8" t="str">
+        <f>IF(LEN(Experiment!AE21)=0,"",Experiment!AE21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="7" t="str">
+        <f>IF(LEN(Experiment!AF21)=0,"",Experiment!AF21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="29" t="str">
+        <f>IF(LEN(Experiment!AG21)=0,"",Experiment!AG21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A22" t="str">
+        <f>IF(Experiment!AH22="","",Experiment!AH22)</f>
+        <v/>
+      </c>
+      <c r="B22" s="12">
+        <v>21</v>
+      </c>
+      <c r="C22" s="8" t="str">
+        <f>IF(LEN(Experiment!AE22)=0,"",Experiment!AE22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="7" t="str">
+        <f>IF(LEN(Experiment!AF22)=0,"",Experiment!AF22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="29" t="str">
+        <f>IF(LEN(Experiment!AG22)=0,"",Experiment!AG22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="11"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A23" t="str">
+        <f>IF(Experiment!AH23="","",Experiment!AH23)</f>
+        <v/>
+      </c>
+      <c r="B23" s="12">
+        <v>22</v>
+      </c>
+      <c r="C23" s="8" t="str">
+        <f>IF(LEN(Experiment!AE23)=0,"",Experiment!AE23)</f>
+        <v/>
+      </c>
+      <c r="D23" s="7" t="str">
+        <f>IF(LEN(Experiment!AF23)=0,"",Experiment!AF23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="29" t="str">
+        <f>IF(LEN(Experiment!AG23)=0,"",Experiment!AG23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="11"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A24" t="str">
+        <f>IF(Experiment!AH24="","",Experiment!AH24)</f>
+        <v/>
+      </c>
+      <c r="B24" s="12">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8" t="str">
+        <f>IF(LEN(Experiment!AE24)=0,"",Experiment!AE24)</f>
+        <v/>
+      </c>
+      <c r="D24" s="7" t="str">
+        <f>IF(LEN(Experiment!AF24)=0,"",Experiment!AF24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="29" t="str">
+        <f>IF(LEN(Experiment!AG24)=0,"",Experiment!AG24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="11"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A25" t="str">
+        <f>IF(Experiment!AH25="","",Experiment!AH25)</f>
+        <v/>
+      </c>
+      <c r="B25" s="12">
+        <v>24</v>
+      </c>
+      <c r="C25" s="8" t="str">
+        <f>IF(LEN(Experiment!AE25)=0,"",Experiment!AE25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="7" t="str">
+        <f>IF(LEN(Experiment!AF25)=0,"",Experiment!AF25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="29" t="str">
+        <f>IF(LEN(Experiment!AG25)=0,"",Experiment!AG25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="11"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A26" t="str">
+        <f>IF(Experiment!AH26="","",Experiment!AH26)</f>
+        <v/>
+      </c>
+      <c r="B26" s="12">
+        <v>25</v>
+      </c>
+      <c r="C26" s="8" t="str">
+        <f>IF(LEN(Experiment!AE26)=0,"",Experiment!AE26)</f>
+        <v/>
+      </c>
+      <c r="D26" s="7" t="str">
+        <f>IF(LEN(Experiment!AF26)=0,"",Experiment!AF26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="29" t="str">
+        <f>IF(LEN(Experiment!AG26)=0,"",Experiment!AG26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="11"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A27" t="str">
+        <f>IF(Experiment!AH27="","",Experiment!AH27)</f>
+        <v/>
+      </c>
+      <c r="B27" s="12">
+        <v>26</v>
+      </c>
+      <c r="C27" s="8" t="str">
+        <f>IF(LEN(Experiment!AE27)=0,"",Experiment!AE27)</f>
+        <v/>
+      </c>
+      <c r="D27" s="7" t="str">
+        <f>IF(LEN(Experiment!AF27)=0,"",Experiment!AF27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="29" t="str">
+        <f>IF(LEN(Experiment!AG27)=0,"",Experiment!AG27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="11"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A28" t="str">
+        <f>IF(Experiment!AH28="","",Experiment!AH28)</f>
+        <v/>
+      </c>
+      <c r="B28" s="12">
+        <v>27</v>
+      </c>
+      <c r="C28" s="8" t="str">
+        <f>IF(LEN(Experiment!AE28)=0,"",Experiment!AE28)</f>
+        <v/>
+      </c>
+      <c r="D28" s="7" t="str">
+        <f>IF(LEN(Experiment!AF28)=0,"",Experiment!AF28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="29" t="str">
+        <f>IF(LEN(Experiment!AG28)=0,"",Experiment!AG28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="11"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A29" t="str">
+        <f>IF(Experiment!AH29="","",Experiment!AH29)</f>
+        <v/>
+      </c>
+      <c r="B29" s="12">
+        <v>28</v>
+      </c>
+      <c r="C29" s="8" t="str">
+        <f>IF(LEN(Experiment!AE29)=0,"",Experiment!AE29)</f>
+        <v/>
+      </c>
+      <c r="D29" s="7" t="str">
+        <f>IF(LEN(Experiment!AF29)=0,"",Experiment!AF29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="29" t="str">
+        <f>IF(LEN(Experiment!AG29)=0,"",Experiment!AG29)</f>
+        <v/>
+      </c>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="11"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A30" t="str">
+        <f>IF(Experiment!AH30="","",Experiment!AH30)</f>
+        <v/>
+      </c>
+      <c r="B30" s="12">
+        <v>29</v>
+      </c>
+      <c r="C30" s="8" t="str">
+        <f>IF(LEN(Experiment!AE30)=0,"",Experiment!AE30)</f>
+        <v/>
+      </c>
+      <c r="D30" s="7" t="str">
+        <f>IF(LEN(Experiment!AF30)=0,"",Experiment!AF30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="29" t="str">
+        <f>IF(LEN(Experiment!AG30)=0,"",Experiment!AG30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="11"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A31" t="str">
+        <f>IF(Experiment!AH31="","",Experiment!AH31)</f>
+        <v/>
+      </c>
+      <c r="B31" s="12">
+        <v>30</v>
+      </c>
+      <c r="C31" s="8" t="str">
+        <f>IF(LEN(Experiment!AE31)=0,"",Experiment!AE31)</f>
+        <v/>
+      </c>
+      <c r="D31" s="7" t="str">
+        <f>IF(LEN(Experiment!AF31)=0,"",Experiment!AF31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="29" t="str">
+        <f>IF(LEN(Experiment!AG31)=0,"",Experiment!AG31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="11"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A32" t="str">
+        <f>IF(Experiment!AH32="","",Experiment!AH32)</f>
+        <v/>
+      </c>
+      <c r="B32" s="12">
+        <v>31</v>
+      </c>
+      <c r="C32" s="8" t="str">
+        <f>IF(LEN(Experiment!AE32)=0,"",Experiment!AE32)</f>
+        <v/>
+      </c>
+      <c r="D32" s="7" t="str">
+        <f>IF(LEN(Experiment!AF32)=0,"",Experiment!AF32)</f>
+        <v/>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="29" t="str">
+        <f>IF(LEN(Experiment!AG32)=0,"",Experiment!AG32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="11"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A33" t="str">
+        <f>IF(Experiment!AH33="","",Experiment!AH33)</f>
+        <v/>
+      </c>
+      <c r="B33" s="12">
+        <v>32</v>
+      </c>
+      <c r="C33" s="8" t="str">
+        <f>IF(LEN(Experiment!AE33)=0,"",Experiment!AE33)</f>
+        <v/>
+      </c>
+      <c r="D33" s="7" t="str">
+        <f>IF(LEN(Experiment!AF33)=0,"",Experiment!AF33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="29" t="str">
+        <f>IF(LEN(Experiment!AG33)=0,"",Experiment!AG33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="11"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A34" t="str">
+        <f>IF(Experiment!AH34="","",Experiment!AH34)</f>
+        <v/>
+      </c>
+      <c r="B34" s="12">
+        <v>33</v>
+      </c>
+      <c r="C34" s="8" t="str">
+        <f>IF(LEN(Experiment!AE34)=0,"",Experiment!AE34)</f>
+        <v/>
+      </c>
+      <c r="D34" s="7" t="str">
+        <f>IF(LEN(Experiment!AF34)=0,"",Experiment!AF34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="30"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="29" t="str">
+        <f>IF(LEN(Experiment!AG34)=0,"",Experiment!AG34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="11"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A35" t="str">
+        <f>IF(Experiment!AH35="","",Experiment!AH35)</f>
+        <v/>
+      </c>
+      <c r="B35" s="12">
+        <v>34</v>
+      </c>
+      <c r="C35" s="8" t="str">
+        <f>IF(LEN(Experiment!AE35)=0,"",Experiment!AE35)</f>
+        <v/>
+      </c>
+      <c r="D35" s="7" t="str">
+        <f>IF(LEN(Experiment!AF35)=0,"",Experiment!AF35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="30"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="29" t="str">
+        <f>IF(LEN(Experiment!AG35)=0,"",Experiment!AG35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="11"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A36" t="str">
+        <f>IF(Experiment!AH36="","",Experiment!AH36)</f>
+        <v/>
+      </c>
+      <c r="B36" s="12">
+        <v>35</v>
+      </c>
+      <c r="C36" s="8" t="str">
+        <f>IF(LEN(Experiment!AE36)=0,"",Experiment!AE36)</f>
+        <v/>
+      </c>
+      <c r="D36" s="7" t="str">
+        <f>IF(LEN(Experiment!AF36)=0,"",Experiment!AF36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="29" t="str">
+        <f>IF(LEN(Experiment!AG36)=0,"",Experiment!AG36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="12"/>
+      <c r="P36" s="11"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A37" t="str">
+        <f>IF(Experiment!AH37="","",Experiment!AH37)</f>
+        <v/>
+      </c>
+      <c r="B37" s="12">
+        <v>36</v>
+      </c>
+      <c r="C37" s="8" t="str">
+        <f>IF(LEN(Experiment!AE37)=0,"",Experiment!AE37)</f>
+        <v/>
+      </c>
+      <c r="D37" s="7" t="str">
+        <f>IF(LEN(Experiment!AF37)=0,"",Experiment!AF37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="30"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="29" t="str">
+        <f>IF(LEN(Experiment!AG37)=0,"",Experiment!AG37)</f>
+        <v/>
+      </c>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="11"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A38" t="str">
+        <f>IF(Experiment!AH38="","",Experiment!AH38)</f>
+        <v/>
+      </c>
+      <c r="B38" s="12">
+        <v>37</v>
+      </c>
+      <c r="C38" s="8" t="str">
+        <f>IF(LEN(Experiment!AE38)=0,"",Experiment!AE38)</f>
+        <v/>
+      </c>
+      <c r="D38" s="7" t="str">
+        <f>IF(LEN(Experiment!AF38)=0,"",Experiment!AF38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="29" t="str">
+        <f>IF(LEN(Experiment!AG38)=0,"",Experiment!AG38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="11"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A39" t="str">
+        <f>IF(Experiment!AH39="","",Experiment!AH39)</f>
+        <v/>
+      </c>
+      <c r="B39" s="12">
+        <v>38</v>
+      </c>
+      <c r="C39" s="8" t="str">
+        <f>IF(LEN(Experiment!AE39)=0,"",Experiment!AE39)</f>
+        <v/>
+      </c>
+      <c r="D39" s="7" t="str">
+        <f>IF(LEN(Experiment!AF39)=0,"",Experiment!AF39)</f>
+        <v/>
+      </c>
+      <c r="E39" s="30"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="29" t="str">
+        <f>IF(LEN(Experiment!AG39)=0,"",Experiment!AG39)</f>
+        <v/>
+      </c>
+      <c r="N39" s="12"/>
+      <c r="O39" s="12"/>
+      <c r="P39" s="11"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A40" t="str">
+        <f>IF(Experiment!AH40="","",Experiment!AH40)</f>
+        <v/>
+      </c>
+      <c r="B40" s="12">
+        <v>39</v>
+      </c>
+      <c r="C40" s="8" t="str">
+        <f>IF(LEN(Experiment!AE40)=0,"",Experiment!AE40)</f>
+        <v/>
+      </c>
+      <c r="D40" s="7" t="str">
+        <f>IF(LEN(Experiment!AF40)=0,"",Experiment!AF40)</f>
+        <v/>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="29" t="str">
+        <f>IF(LEN(Experiment!AG40)=0,"",Experiment!AG40)</f>
+        <v/>
+      </c>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="11"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A41" t="str">
+        <f>IF(Experiment!AH41="","",Experiment!AH41)</f>
+        <v/>
+      </c>
+      <c r="B41" s="12">
+        <v>40</v>
+      </c>
+      <c r="C41" s="8" t="str">
+        <f>IF(LEN(Experiment!AE41)=0,"",Experiment!AE41)</f>
+        <v/>
+      </c>
+      <c r="D41" s="7" t="str">
+        <f>IF(LEN(Experiment!AF41)=0,"",Experiment!AF41)</f>
+        <v/>
+      </c>
+      <c r="E41" s="30"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="29" t="str">
+        <f>IF(LEN(Experiment!AG41)=0,"",Experiment!AG41)</f>
+        <v/>
+      </c>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
+      <c r="P41" s="11"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A42" t="str">
+        <f>IF(Experiment!AH42="","",Experiment!AH42)</f>
+        <v/>
+      </c>
+      <c r="B42" s="12">
+        <v>41</v>
+      </c>
+      <c r="C42" s="8" t="str">
+        <f>IF(LEN(Experiment!AE42)=0,"",Experiment!AE42)</f>
+        <v/>
+      </c>
+      <c r="D42" s="7" t="str">
+        <f>IF(LEN(Experiment!AF42)=0,"",Experiment!AF42)</f>
+        <v/>
+      </c>
+      <c r="E42" s="30"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="29" t="str">
+        <f>IF(LEN(Experiment!AG42)=0,"",Experiment!AG42)</f>
+        <v/>
+      </c>
+      <c r="N42" s="12"/>
+      <c r="O42" s="12"/>
+      <c r="P42" s="11"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A43" t="str">
+        <f>IF(Experiment!AH43="","",Experiment!AH43)</f>
+        <v/>
+      </c>
+      <c r="B43" s="12">
+        <v>42</v>
+      </c>
+      <c r="C43" s="8" t="str">
+        <f>IF(LEN(Experiment!AE43)=0,"",Experiment!AE43)</f>
+        <v/>
+      </c>
+      <c r="D43" s="7" t="str">
+        <f>IF(LEN(Experiment!AF43)=0,"",Experiment!AF43)</f>
+        <v/>
+      </c>
+      <c r="E43" s="30"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="29" t="str">
+        <f>IF(LEN(Experiment!AG43)=0,"",Experiment!AG43)</f>
+        <v/>
+      </c>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
+      <c r="P43" s="11"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A44" t="str">
+        <f>IF(Experiment!AH44="","",Experiment!AH44)</f>
+        <v/>
+      </c>
+      <c r="B44" s="12">
+        <v>43</v>
+      </c>
+      <c r="C44" s="8" t="str">
+        <f>IF(LEN(Experiment!AE44)=0,"",Experiment!AE44)</f>
+        <v/>
+      </c>
+      <c r="D44" s="7" t="str">
+        <f>IF(LEN(Experiment!AF44)=0,"",Experiment!AF44)</f>
+        <v/>
+      </c>
+      <c r="E44" s="30"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="29" t="str">
+        <f>IF(LEN(Experiment!AG44)=0,"",Experiment!AG44)</f>
+        <v/>
+      </c>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12"/>
+      <c r="P44" s="11"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A45" t="str">
+        <f>IF(Experiment!AH45="","",Experiment!AH45)</f>
+        <v/>
+      </c>
+      <c r="B45" s="12">
+        <v>44</v>
+      </c>
+      <c r="C45" s="8" t="str">
+        <f>IF(LEN(Experiment!AE45)=0,"",Experiment!AE45)</f>
+        <v/>
+      </c>
+      <c r="D45" s="7" t="str">
+        <f>IF(LEN(Experiment!AF45)=0,"",Experiment!AF45)</f>
+        <v/>
+      </c>
+      <c r="E45" s="30"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="29" t="str">
+        <f>IF(LEN(Experiment!AG45)=0,"",Experiment!AG45)</f>
+        <v/>
+      </c>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="11"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A46" t="str">
+        <f>IF(Experiment!AH46="","",Experiment!AH46)</f>
+        <v/>
+      </c>
+      <c r="B46" s="12">
+        <v>45</v>
+      </c>
+      <c r="C46" s="8" t="str">
+        <f>IF(LEN(Experiment!AE46)=0,"",Experiment!AE46)</f>
+        <v/>
+      </c>
+      <c r="D46" s="7" t="str">
+        <f>IF(LEN(Experiment!AF46)=0,"",Experiment!AF46)</f>
+        <v/>
+      </c>
+      <c r="E46" s="30"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="29" t="str">
+        <f>IF(LEN(Experiment!AG46)=0,"",Experiment!AG46)</f>
+        <v/>
+      </c>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="11"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A47" t="str">
+        <f>IF(Experiment!AH47="","",Experiment!AH47)</f>
+        <v/>
+      </c>
+      <c r="B47" s="12">
+        <v>46</v>
+      </c>
+      <c r="C47" s="8" t="str">
+        <f>IF(LEN(Experiment!AE47)=0,"",Experiment!AE47)</f>
+        <v/>
+      </c>
+      <c r="D47" s="7" t="str">
+        <f>IF(LEN(Experiment!AF47)=0,"",Experiment!AF47)</f>
+        <v/>
+      </c>
+      <c r="E47" s="30"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="29" t="str">
+        <f>IF(LEN(Experiment!AG47)=0,"",Experiment!AG47)</f>
+        <v/>
+      </c>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="11"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A48" t="str">
+        <f>IF(Experiment!AH48="","",Experiment!AH48)</f>
+        <v/>
+      </c>
+      <c r="B48" s="12">
+        <v>47</v>
+      </c>
+      <c r="C48" s="8" t="str">
+        <f>IF(LEN(Experiment!AE48)=0,"",Experiment!AE48)</f>
+        <v/>
+      </c>
+      <c r="D48" s="7" t="str">
+        <f>IF(LEN(Experiment!AF48)=0,"",Experiment!AF48)</f>
+        <v/>
+      </c>
+      <c r="E48" s="31"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="29" t="str">
+        <f>IF(LEN(Experiment!AG48)=0,"",Experiment!AG48)</f>
+        <v/>
+      </c>
+      <c r="N48" s="12"/>
+      <c r="O48" s="12"/>
+      <c r="P48" s="11"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A49" t="str">
+        <f>IF(Experiment!AH49="","",Experiment!AH49)</f>
+        <v/>
+      </c>
+      <c r="B49" s="12">
+        <v>48</v>
+      </c>
+      <c r="C49" s="8" t="str">
+        <f>IF(LEN(Experiment!AE49)=0,"",Experiment!AE49)</f>
+        <v/>
+      </c>
+      <c r="D49" s="7" t="str">
+        <f>IF(LEN(Experiment!AF49)=0,"",Experiment!AF49)</f>
+        <v/>
+      </c>
+      <c r="E49" s="31"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="29" t="str">
+        <f>IF(LEN(Experiment!AG49)=0,"",Experiment!AG49)</f>
+        <v/>
+      </c>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
+      <c r="P49" s="11"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A50" t="str">
+        <f>IF(Experiment!AH50="","",Experiment!AH50)</f>
+        <v/>
+      </c>
+      <c r="B50" s="12">
+        <v>49</v>
+      </c>
+      <c r="C50" s="8" t="str">
+        <f>IF(LEN(Experiment!AE50)=0,"",Experiment!AE50)</f>
+        <v/>
+      </c>
+      <c r="D50" s="7" t="str">
+        <f>IF(LEN(Experiment!AF50)=0,"",Experiment!AF50)</f>
+        <v/>
+      </c>
+      <c r="E50" s="31"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="29" t="str">
+        <f>IF(LEN(Experiment!AG50)=0,"",Experiment!AG50)</f>
+        <v/>
+      </c>
+      <c r="N50" s="12"/>
+      <c r="O50" s="12"/>
+      <c r="P50" s="11"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A51" t="str">
+        <f>IF(Experiment!AH51="","",Experiment!AH51)</f>
+        <v/>
+      </c>
+      <c r="B51" s="20">
         <v>50</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A2" s="12">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="str">
-        <f>IF(LEN(User!AE2)=0,"",User!AE2)</f>
-        <v/>
-      </c>
-      <c r="C2" s="7" t="str">
-        <f>IF(LEN(User!AF2)=0,"",User!AF2)</f>
-        <v/>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="29" t="str">
-        <f>IF(LEN(User!AG2)=0,"",User!AG2)</f>
-        <v/>
-      </c>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="11"/>
-      <c r="Q2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="str">
-        <f>IF(LEN(User!AE3)=0,"",User!AE3)</f>
-        <v/>
-      </c>
-      <c r="C3" s="7" t="str">
-        <f>IF(LEN(User!AF3)=0,"",User!AF3)</f>
-        <v/>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="29" t="str">
-        <f>IF(LEN(User!AG3)=0,"",User!AG3)</f>
-        <v/>
-      </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="str">
-        <f>IF(LEN(User!AE4)=0,"",User!AE4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="7" t="str">
-        <f>IF(LEN(User!AF4)=0,"",User!AF4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="29" t="str">
-        <f>IF(LEN(User!AG4)=0,"",User!AG4)</f>
-        <v/>
-      </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="11"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="24"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A5" s="12">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="str">
-        <f>IF(LEN(User!AE5)=0,"",User!AE5)</f>
-        <v/>
-      </c>
-      <c r="C5" s="7" t="str">
-        <f>IF(LEN(User!AF5)=0,"",User!AF5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="29" t="str">
-        <f>IF(LEN(User!AG5)=0,"",User!AG5)</f>
-        <v/>
-      </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="11"/>
-      <c r="Q5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6" s="12">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="str">
-        <f>IF(LEN(User!AE6)=0,"",User!AE6)</f>
-        <v/>
-      </c>
-      <c r="C6" s="7" t="str">
-        <f>IF(LEN(User!AF6)=0,"",User!AF6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="29" t="str">
-        <f>IF(LEN(User!AG6)=0,"",User!AG6)</f>
-        <v/>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="11"/>
-      <c r="Q6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" s="32"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7" s="12">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="str">
-        <f>IF(LEN(User!AE7)=0,"",User!AE7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="7" t="str">
-        <f>IF(LEN(User!AF7)=0,"",User!AF7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="29" t="str">
-        <f>IF(LEN(User!AG7)=0,"",User!AG7)</f>
-        <v/>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="11"/>
-      <c r="Q7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R7" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8" s="12">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="str">
-        <f>IF(LEN(User!AE8)=0,"",User!AE8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="str">
-        <f>IF(LEN(User!AF8)=0,"",User!AF8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="29" t="str">
-        <f>IF(LEN(User!AG8)=0,"",User!AG8)</f>
-        <v/>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="11"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9" s="12">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="str">
-        <f>IF(LEN(User!AE9)=0,"",User!AE9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="str">
-        <f>IF(LEN(User!AF9)=0,"",User!AF9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="29" t="str">
-        <f>IF(LEN(User!AG9)=0,"",User!AG9)</f>
-        <v/>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="11"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A10" s="12">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="str">
-        <f>IF(LEN(User!AE10)=0,"",User!AE10)</f>
-        <v/>
-      </c>
-      <c r="C10" s="7" t="str">
-        <f>IF(LEN(User!AF10)=0,"",User!AF10)</f>
-        <v/>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="29" t="str">
-        <f>IF(LEN(User!AG10)=0,"",User!AG10)</f>
-        <v/>
-      </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="11"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="str">
-        <f>IF(LEN(User!AE11)=0,"",User!AE11)</f>
-        <v/>
-      </c>
-      <c r="C11" s="7" t="str">
-        <f>IF(LEN(User!AF11)=0,"",User!AF11)</f>
-        <v/>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="29" t="str">
-        <f>IF(LEN(User!AG11)=0,"",User!AG11)</f>
-        <v/>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A12" s="12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="str">
-        <f>IF(LEN(User!AE12)=0,"",User!AE12)</f>
-        <v/>
-      </c>
-      <c r="C12" s="7" t="str">
-        <f>IF(LEN(User!AF12)=0,"",User!AF12)</f>
-        <v/>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="29" t="str">
-        <f>IF(LEN(User!AG12)=0,"",User!AG12)</f>
-        <v/>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="11"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13" s="12">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="str">
-        <f>IF(LEN(User!AE13)=0,"",User!AE13)</f>
-        <v/>
-      </c>
-      <c r="C13" s="7" t="str">
-        <f>IF(LEN(User!AF13)=0,"",User!AF13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="29" t="str">
-        <f>IF(LEN(User!AG13)=0,"",User!AG13)</f>
-        <v/>
-      </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="11"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A14" s="12">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="str">
-        <f>IF(LEN(User!AE14)=0,"",User!AE14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="7" t="str">
-        <f>IF(LEN(User!AF14)=0,"",User!AF14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="29" t="str">
-        <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
-        <v/>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="11"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="12">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="str">
-        <f>IF(LEN(User!AE15)=0,"",User!AE15)</f>
-        <v/>
-      </c>
-      <c r="C15" s="7" t="str">
-        <f>IF(LEN(User!AF15)=0,"",User!AF15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="29" t="str">
-        <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
-        <v/>
-      </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="11"/>
-    </row>
-    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="12">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="str">
-        <f>IF(LEN(User!AE16)=0,"",User!AE16)</f>
-        <v/>
-      </c>
-      <c r="C16" s="7" t="str">
-        <f>IF(LEN(User!AF16)=0,"",User!AF16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="29" t="str">
-        <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="11"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A17" s="12">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="str">
-        <f>IF(LEN(User!AE17)=0,"",User!AE17)</f>
-        <v/>
-      </c>
-      <c r="C17" s="7" t="str">
-        <f>IF(LEN(User!AF17)=0,"",User!AF17)</f>
-        <v/>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="29" t="str">
-        <f>IF(LEN(User!AG17)=0,"",User!AG17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="11"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A18" s="12">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="str">
-        <f>IF(LEN(User!AE18)=0,"",User!AE18)</f>
-        <v/>
-      </c>
-      <c r="C18" s="7" t="str">
-        <f>IF(LEN(User!AF18)=0,"",User!AF18)</f>
-        <v/>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="29" t="str">
-        <f>IF(LEN(User!AG18)=0,"",User!AG18)</f>
-        <v/>
-      </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="11"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A19" s="12">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="str">
-        <f>IF(LEN(User!AE19)=0,"",User!AE19)</f>
-        <v/>
-      </c>
-      <c r="C19" s="7" t="str">
-        <f>IF(LEN(User!AF19)=0,"",User!AF19)</f>
-        <v/>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="29" t="str">
-        <f>IF(LEN(User!AG19)=0,"",User!AG19)</f>
-        <v/>
-      </c>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="11"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A20" s="12">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="str">
-        <f>IF(LEN(User!AE20)=0,"",User!AE20)</f>
-        <v/>
-      </c>
-      <c r="C20" s="7" t="str">
-        <f>IF(LEN(User!AF20)=0,"",User!AF20)</f>
-        <v/>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="29" t="str">
-        <f>IF(LEN(User!AG20)=0,"",User!AG20)</f>
-        <v/>
-      </c>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="11"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21" s="12">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="str">
-        <f>IF(LEN(User!AE21)=0,"",User!AE21)</f>
-        <v/>
-      </c>
-      <c r="C21" s="7" t="str">
-        <f>IF(LEN(User!AF21)=0,"",User!AF21)</f>
-        <v/>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="29" t="str">
-        <f>IF(LEN(User!AG21)=0,"",User!AG21)</f>
-        <v/>
-      </c>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="11"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A22" s="12">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="str">
-        <f>IF(LEN(User!AE22)=0,"",User!AE22)</f>
-        <v/>
-      </c>
-      <c r="C22" s="7" t="str">
-        <f>IF(LEN(User!AF22)=0,"",User!AF22)</f>
-        <v/>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="29" t="str">
-        <f>IF(LEN(User!AG22)=0,"",User!AG22)</f>
-        <v/>
-      </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="11"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A23" s="12">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="str">
-        <f>IF(LEN(User!AE23)=0,"",User!AE23)</f>
-        <v/>
-      </c>
-      <c r="C23" s="7" t="str">
-        <f>IF(LEN(User!AF23)=0,"",User!AF23)</f>
-        <v/>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="29" t="str">
-        <f>IF(LEN(User!AG23)=0,"",User!AG23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="11"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A24" s="12">
-        <v>23</v>
-      </c>
-      <c r="B24" s="8" t="str">
-        <f>IF(LEN(User!AE24)=0,"",User!AE24)</f>
-        <v/>
-      </c>
-      <c r="C24" s="7" t="str">
-        <f>IF(LEN(User!AF24)=0,"",User!AF24)</f>
-        <v/>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="29" t="str">
-        <f>IF(LEN(User!AG24)=0,"",User!AG24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="11"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A25" s="12">
-        <v>24</v>
-      </c>
-      <c r="B25" s="8" t="str">
-        <f>IF(LEN(User!AE25)=0,"",User!AE25)</f>
-        <v/>
-      </c>
-      <c r="C25" s="7" t="str">
-        <f>IF(LEN(User!AF25)=0,"",User!AF25)</f>
-        <v/>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="29" t="str">
-        <f>IF(LEN(User!AG25)=0,"",User!AG25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="11"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A26" s="12">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="str">
-        <f>IF(LEN(User!AE26)=0,"",User!AE26)</f>
-        <v/>
-      </c>
-      <c r="C26" s="7" t="str">
-        <f>IF(LEN(User!AF26)=0,"",User!AF26)</f>
-        <v/>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="29" t="str">
-        <f>IF(LEN(User!AG26)=0,"",User!AG26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="11"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A27" s="12">
-        <v>26</v>
-      </c>
-      <c r="B27" s="8" t="str">
-        <f>IF(LEN(User!AE27)=0,"",User!AE27)</f>
-        <v/>
-      </c>
-      <c r="C27" s="7" t="str">
-        <f>IF(LEN(User!AF27)=0,"",User!AF27)</f>
-        <v/>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="29" t="str">
-        <f>IF(LEN(User!AG27)=0,"",User!AG27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="11"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A28" s="12">
-        <v>27</v>
-      </c>
-      <c r="B28" s="8" t="str">
-        <f>IF(LEN(User!AE28)=0,"",User!AE28)</f>
-        <v/>
-      </c>
-      <c r="C28" s="7" t="str">
-        <f>IF(LEN(User!AF28)=0,"",User!AF28)</f>
-        <v/>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="29" t="str">
-        <f>IF(LEN(User!AG28)=0,"",User!AG28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="11"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A29" s="12">
-        <v>28</v>
-      </c>
-      <c r="B29" s="8" t="str">
-        <f>IF(LEN(User!AE29)=0,"",User!AE29)</f>
-        <v/>
-      </c>
-      <c r="C29" s="7" t="str">
-        <f>IF(LEN(User!AF29)=0,"",User!AF29)</f>
-        <v/>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="29" t="str">
-        <f>IF(LEN(User!AG29)=0,"",User!AG29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="11"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A30" s="12">
-        <v>29</v>
-      </c>
-      <c r="B30" s="8" t="str">
-        <f>IF(LEN(User!AE30)=0,"",User!AE30)</f>
-        <v/>
-      </c>
-      <c r="C30" s="7" t="str">
-        <f>IF(LEN(User!AF30)=0,"",User!AF30)</f>
-        <v/>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="29" t="str">
-        <f>IF(LEN(User!AG30)=0,"",User!AG30)</f>
-        <v/>
-      </c>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="11"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A31" s="12">
-        <v>30</v>
-      </c>
-      <c r="B31" s="8" t="str">
-        <f>IF(LEN(User!AE31)=0,"",User!AE31)</f>
-        <v/>
-      </c>
-      <c r="C31" s="7" t="str">
-        <f>IF(LEN(User!AF31)=0,"",User!AF31)</f>
-        <v/>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="29" t="str">
-        <f>IF(LEN(User!AG31)=0,"",User!AG31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="11"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A32" s="12">
-        <v>31</v>
-      </c>
-      <c r="B32" s="8" t="str">
-        <f>IF(LEN(User!AE32)=0,"",User!AE32)</f>
-        <v/>
-      </c>
-      <c r="C32" s="7" t="str">
-        <f>IF(LEN(User!AF32)=0,"",User!AF32)</f>
-        <v/>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="29" t="str">
-        <f>IF(LEN(User!AG32)=0,"",User!AG32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="11"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A33" s="12">
-        <v>32</v>
-      </c>
-      <c r="B33" s="8" t="str">
-        <f>IF(LEN(User!AE33)=0,"",User!AE33)</f>
-        <v/>
-      </c>
-      <c r="C33" s="7" t="str">
-        <f>IF(LEN(User!AF33)=0,"",User!AF33)</f>
-        <v/>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="29" t="str">
-        <f>IF(LEN(User!AG33)=0,"",User!AG33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="11"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A34" s="12">
-        <v>33</v>
-      </c>
-      <c r="B34" s="8" t="str">
-        <f>IF(LEN(User!AE34)=0,"",User!AE34)</f>
-        <v/>
-      </c>
-      <c r="C34" s="7" t="str">
-        <f>IF(LEN(User!AF34)=0,"",User!AF34)</f>
-        <v/>
-      </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="29" t="str">
-        <f>IF(LEN(User!AG34)=0,"",User!AG34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="11"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A35" s="12">
-        <v>34</v>
-      </c>
-      <c r="B35" s="8" t="str">
-        <f>IF(LEN(User!AE35)=0,"",User!AE35)</f>
-        <v/>
-      </c>
-      <c r="C35" s="7" t="str">
-        <f>IF(LEN(User!AF35)=0,"",User!AF35)</f>
-        <v/>
-      </c>
-      <c r="D35" s="30"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="29" t="str">
-        <f>IF(LEN(User!AG35)=0,"",User!AG35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="11"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A36" s="12">
-        <v>35</v>
-      </c>
-      <c r="B36" s="8" t="str">
-        <f>IF(LEN(User!AE36)=0,"",User!AE36)</f>
-        <v/>
-      </c>
-      <c r="C36" s="7" t="str">
-        <f>IF(LEN(User!AF36)=0,"",User!AF36)</f>
-        <v/>
-      </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="29" t="str">
-        <f>IF(LEN(User!AG36)=0,"",User!AG36)</f>
-        <v/>
-      </c>
-      <c r="N36" s="12"/>
-      <c r="O36" s="11"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A37" s="12">
-        <v>36</v>
-      </c>
-      <c r="B37" s="8" t="str">
-        <f>IF(LEN(User!AE37)=0,"",User!AE37)</f>
-        <v/>
-      </c>
-      <c r="C37" s="7" t="str">
-        <f>IF(LEN(User!AF37)=0,"",User!AF37)</f>
-        <v/>
-      </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="29" t="str">
-        <f>IF(LEN(User!AG37)=0,"",User!AG37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="11"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A38" s="12">
-        <v>37</v>
-      </c>
-      <c r="B38" s="8" t="str">
-        <f>IF(LEN(User!AE38)=0,"",User!AE38)</f>
-        <v/>
-      </c>
-      <c r="C38" s="7" t="str">
-        <f>IF(LEN(User!AF38)=0,"",User!AF38)</f>
-        <v/>
-      </c>
-      <c r="D38" s="30"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="29" t="str">
-        <f>IF(LEN(User!AG38)=0,"",User!AG38)</f>
-        <v/>
-      </c>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="11"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A39" s="12">
-        <v>38</v>
-      </c>
-      <c r="B39" s="8" t="str">
-        <f>IF(LEN(User!AE39)=0,"",User!AE39)</f>
-        <v/>
-      </c>
-      <c r="C39" s="7" t="str">
-        <f>IF(LEN(User!AF39)=0,"",User!AF39)</f>
-        <v/>
-      </c>
-      <c r="D39" s="30"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="29" t="str">
-        <f>IF(LEN(User!AG39)=0,"",User!AG39)</f>
-        <v/>
-      </c>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="11"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A40" s="12">
-        <v>39</v>
-      </c>
-      <c r="B40" s="8" t="str">
-        <f>IF(LEN(User!AE40)=0,"",User!AE40)</f>
-        <v/>
-      </c>
-      <c r="C40" s="7" t="str">
-        <f>IF(LEN(User!AF40)=0,"",User!AF40)</f>
-        <v/>
-      </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="29" t="str">
-        <f>IF(LEN(User!AG40)=0,"",User!AG40)</f>
-        <v/>
-      </c>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="11"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A41" s="12">
-        <v>40</v>
-      </c>
-      <c r="B41" s="8" t="str">
-        <f>IF(LEN(User!AE41)=0,"",User!AE41)</f>
-        <v/>
-      </c>
-      <c r="C41" s="7" t="str">
-        <f>IF(LEN(User!AF41)=0,"",User!AF41)</f>
-        <v/>
-      </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="29" t="str">
-        <f>IF(LEN(User!AG41)=0,"",User!AG41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="12"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="11"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A42" s="12">
-        <v>41</v>
-      </c>
-      <c r="B42" s="8" t="str">
-        <f>IF(LEN(User!AE42)=0,"",User!AE42)</f>
-        <v/>
-      </c>
-      <c r="C42" s="7" t="str">
-        <f>IF(LEN(User!AF42)=0,"",User!AF42)</f>
-        <v/>
-      </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="29" t="str">
-        <f>IF(LEN(User!AG42)=0,"",User!AG42)</f>
-        <v/>
-      </c>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="11"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A43" s="12">
-        <v>42</v>
-      </c>
-      <c r="B43" s="8" t="str">
-        <f>IF(LEN(User!AE43)=0,"",User!AE43)</f>
-        <v/>
-      </c>
-      <c r="C43" s="7" t="str">
-        <f>IF(LEN(User!AF43)=0,"",User!AF43)</f>
-        <v/>
-      </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="29" t="str">
-        <f>IF(LEN(User!AG43)=0,"",User!AG43)</f>
-        <v/>
-      </c>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="11"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A44" s="12">
-        <v>43</v>
-      </c>
-      <c r="B44" s="8" t="str">
-        <f>IF(LEN(User!AE44)=0,"",User!AE44)</f>
-        <v/>
-      </c>
-      <c r="C44" s="7" t="str">
-        <f>IF(LEN(User!AF44)=0,"",User!AF44)</f>
-        <v/>
-      </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="29" t="str">
-        <f>IF(LEN(User!AG44)=0,"",User!AG44)</f>
-        <v/>
-      </c>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="11"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A45" s="12">
-        <v>44</v>
-      </c>
-      <c r="B45" s="8" t="str">
-        <f>IF(LEN(User!AE45)=0,"",User!AE45)</f>
-        <v/>
-      </c>
-      <c r="C45" s="7" t="str">
-        <f>IF(LEN(User!AF45)=0,"",User!AF45)</f>
-        <v/>
-      </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="29" t="str">
-        <f>IF(LEN(User!AG45)=0,"",User!AG45)</f>
-        <v/>
-      </c>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="11"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A46" s="12">
-        <v>45</v>
-      </c>
-      <c r="B46" s="8" t="str">
-        <f>IF(LEN(User!AE46)=0,"",User!AE46)</f>
-        <v/>
-      </c>
-      <c r="C46" s="7" t="str">
-        <f>IF(LEN(User!AF46)=0,"",User!AF46)</f>
-        <v/>
-      </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="29" t="str">
-        <f>IF(LEN(User!AG46)=0,"",User!AG46)</f>
-        <v/>
-      </c>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="11"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A47" s="12">
-        <v>46</v>
-      </c>
-      <c r="B47" s="8" t="str">
-        <f>IF(LEN(User!AE47)=0,"",User!AE47)</f>
-        <v/>
-      </c>
-      <c r="C47" s="7" t="str">
-        <f>IF(LEN(User!AF47)=0,"",User!AF47)</f>
-        <v/>
-      </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="29" t="str">
-        <f>IF(LEN(User!AG47)=0,"",User!AG47)</f>
-        <v/>
-      </c>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="11"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A48" s="12">
-        <v>47</v>
-      </c>
-      <c r="B48" s="8" t="str">
-        <f>IF(LEN(User!AE48)=0,"",User!AE48)</f>
-        <v/>
-      </c>
-      <c r="C48" s="7" t="str">
-        <f>IF(LEN(User!AF48)=0,"",User!AF48)</f>
-        <v/>
-      </c>
-      <c r="D48" s="31"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="29" t="str">
-        <f>IF(LEN(User!AG48)=0,"",User!AG48)</f>
-        <v/>
-      </c>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="11"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A49" s="12">
-        <v>48</v>
-      </c>
-      <c r="B49" s="8" t="str">
-        <f>IF(LEN(User!AE49)=0,"",User!AE49)</f>
-        <v/>
-      </c>
-      <c r="C49" s="7" t="str">
-        <f>IF(LEN(User!AF49)=0,"",User!AF49)</f>
-        <v/>
-      </c>
-      <c r="D49" s="31"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="29" t="str">
-        <f>IF(LEN(User!AG49)=0,"",User!AG49)</f>
-        <v/>
-      </c>
-      <c r="M49" s="12"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="11"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A50" s="12">
-        <v>49</v>
-      </c>
-      <c r="B50" s="8" t="str">
-        <f>IF(LEN(User!AE50)=0,"",User!AE50)</f>
-        <v/>
-      </c>
-      <c r="C50" s="7" t="str">
-        <f>IF(LEN(User!AF50)=0,"",User!AF50)</f>
-        <v/>
-      </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="29" t="str">
-        <f>IF(LEN(User!AG50)=0,"",User!AG50)</f>
-        <v/>
-      </c>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="11"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A51" s="20">
-        <v>50</v>
-      </c>
-      <c r="B51" s="17" t="str">
-        <f>IF(LEN(User!AE51)=0,"",User!AE51)</f>
-        <v/>
-      </c>
-      <c r="C51" s="13" t="str">
-        <f>IF(LEN(User!AF51)=0,"",User!AF51)</f>
-        <v/>
-      </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="20"/>
+      <c r="C51" s="17" t="str">
+        <f>IF(LEN(Experiment!AE51)=0,"",Experiment!AE51)</f>
+        <v/>
+      </c>
+      <c r="D51" s="13" t="str">
+        <f>IF(LEN(Experiment!AF51)=0,"",Experiment!AF51)</f>
+        <v/>
+      </c>
+      <c r="E51" s="19"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="43"/>
       <c r="N51" s="20"/>
-      <c r="O51" s="21"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="21"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C51" xr:uid="{187E9458-F80F-4040-ADAB-CFE8AE95B8DD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D51" xr:uid="{187E9458-F80F-4040-ADAB-CFE8AE95B8DD}">
       <formula1>"Condition,QC,Blank,TrueBlank,Lib,SystemValidation,WetQC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5" xr:uid="{FEBF46E2-B8D0-DB4A-AFDC-F2F0CF8E04A9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5" xr:uid="{FEBF46E2-B8D0-DB4A-AFDC-F2F0CF8E04A9}">
       <formula1>"Before,After,(choose)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{38B3635F-E371-C941-A218-633361397008}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2" xr:uid="{38B3635F-E371-C941-A218-633361397008}">
       <formula1>"1 column, 2 column, (choose)"</formula1>
     </dataValidation>
   </dataValidations>
